--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260902.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>8,422,000</t>
+          <t>100,983,502</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>100,983,502</t>
+          <t>8,422,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
